--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NRUnity\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F305164-3811-48B8-89D1-5F085297CA61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400EB44E-C89A-46E8-924E-704BC257DC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="930" windowWidth="26355" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2040" yWindow="645" windowWidth="24285" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -142,10 +142,6 @@
   </si>
   <si>
     <t>string[]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>UseItemParameter</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -189,6 +185,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">SummonMonster </t>
     </r>
@@ -222,6 +219,10 @@
   </si>
   <si>
     <t>mob_bettle_1:2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseItemParameterList</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -571,7 +572,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -580,7 +581,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="firstColumnStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" table="0" count="8" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -825,7 +826,7 @@
         <v>18</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="12.75">
@@ -889,7 +890,7 @@
         <v>33</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1">
@@ -921,7 +922,7 @@
         <v>34</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
@@ -929,7 +930,7 @@
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>26</v>
@@ -960,7 +961,7 @@
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>9</v>
@@ -995,7 +996,7 @@
     </row>
     <row r="7" spans="1:13" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>23</v>
@@ -1057,7 +1058,7 @@
         <v>37</v>
       </c>
       <c r="J8" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NRUnity\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400EB44E-C89A-46E8-924E-704BC257DC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BC141D-B8EC-46B3-B58D-72DE48D27F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2040" yWindow="645" windowWidth="24285" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9210" yWindow="240" windowWidth="19215" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NRUnity\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BC141D-B8EC-46B3-B58D-72DE48D27F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D96DA6D8-5181-42C1-864D-E35F5DE81337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9210" yWindow="240" windowWidth="19215" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5445" yWindow="1560" windowWidth="19215" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="52">
   <si>
     <t>Icon/Icon_Item_Corn</t>
   </si>
@@ -223,6 +223,30 @@
   </si>
   <si>
     <t>UseItemParameterList</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>노말등급의 타워다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Tower_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 타워</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_Tower_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>tower_Black:1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1065,16 +1089,36 @@
       <c r="M8" s="4"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+      <c r="A9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4">
+        <v>50</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>51</v>
+      </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NRUnity\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D96DA6D8-5181-42C1-864D-E35F5DE81337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DAFA39D-11EA-4CA0-BAC8-138F55048432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5445" yWindow="1560" windowWidth="19215" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30615" yWindow="1470" windowWidth="23670" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="78">
   <si>
     <t>Icon/Icon_Item_Corn</t>
   </si>
@@ -248,6 +248,108 @@
   <si>
     <t>tower_Black:1</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Tower_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Tower_3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Tower_4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Tower_5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>레어 타워</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>에픽 타워</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>유니크 타워</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>레전더리 타워</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epic</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unique</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legend</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_Tower_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_Tower_3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_Tower_4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_Tower_5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SummonMonster</t>
+  </si>
+  <si>
+    <t>tower_Blue:1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>tower_Purple:1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>tower_Yellow:1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>tower_Red:1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>레어등급의 타워다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>에픽등급의 타워다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>유니크등급의 타워다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>레전더리등급의 타워다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
   </si>
 </sst>
 </file>
@@ -1124,61 +1226,141 @@
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+      <c r="A10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4">
+        <v>100</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>69</v>
+      </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
+      <c r="A11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="4">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4">
+        <v>200</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>70</v>
+      </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
+      <c r="A12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4">
+        <v>400</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>71</v>
+      </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
+      <c r="A13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4">
+        <v>800</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>72</v>
+      </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NRUnity\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DAFA39D-11EA-4CA0-BAC8-138F55048432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1E0AE6-FBFA-49EA-8252-FDAB9F2DC96F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30615" yWindow="1470" windowWidth="23670" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="885" windowWidth="22035" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="83">
   <si>
     <t>Icon/Icon_Item_Corn</t>
   </si>
@@ -350,6 +350,26 @@
   </si>
   <si>
     <t>Rare</t>
+  </si>
+  <si>
+    <t>Item_Unit_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>전사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>소환하는 전사다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Icon_Item_Unit_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unit_Warrior:1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1355,8 +1375,8 @@
       <c r="H13" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>68</v>
+      <c r="I13" s="17" t="s">
+        <v>37</v>
       </c>
       <c r="J13" s="17" t="s">
         <v>72</v>
@@ -1366,16 +1386,36 @@
       <c r="M13" s="4"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
+      <c r="A14" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4">
+        <v>150</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>82</v>
+      </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -1388,7 +1428,6 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NRUnity\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1E0AE6-FBFA-49EA-8252-FDAB9F2DC96F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75A37B4-26C7-4AEC-9B78-209C4E474E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="885" windowWidth="22035" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1680" yWindow="1335" windowWidth="22035" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -1405,7 +1405,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="4">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H14" s="17" t="s">
         <v>81</v>
